--- a/TS Jatai Ghanam Project/Stas table for TS 5.1 TO 5.7.xlsx
+++ b/TS Jatai Ghanam Project/Stas table for TS 5.1 TO 5.7.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ALL IMP DATA\GitHub\texts\TS Jatai Ghanam Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\texts\TS Jatai Ghanam Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D67B31-A93F-4B03-9899-BD1F13A42DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="5.1" sheetId="15" r:id="rId1"/>
@@ -22,10 +22,19 @@
     <sheet name="5.7" sheetId="21" r:id="rId7"/>
     <sheet name="total 5.1 to 5.7" sheetId="7" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -20668,7 +20677,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="2:12" ht="33" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:12" ht="39" x14ac:dyDescent="0.5">
       <c r="B25" s="10" t="s">
         <v>19</v>
       </c>
@@ -20711,7 +20720,7 @@
         <v>15052</v>
       </c>
     </row>
-    <row r="26" spans="2:12" ht="82.5" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:12" ht="97.5" x14ac:dyDescent="0.5">
       <c r="B26" s="10" t="s">
         <v>21</v>
       </c>
@@ -20754,7 +20763,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="27" spans="2:12" ht="102" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:12" ht="156" x14ac:dyDescent="0.5">
       <c r="B27" s="10" t="s">
         <v>23</v>
       </c>
@@ -20797,7 +20806,7 @@
         <v>2992</v>
       </c>
     </row>
-    <row r="28" spans="2:12" ht="89.25" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:12" ht="136.5" x14ac:dyDescent="0.5">
       <c r="B28" s="10" t="s">
         <v>24</v>
       </c>
@@ -20840,7 +20849,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="2:12" ht="132" x14ac:dyDescent="0.4">
+    <row r="29" spans="2:12" ht="156" x14ac:dyDescent="0.5">
       <c r="B29" s="10" t="s">
         <v>26</v>
       </c>

--- a/TS Jatai Ghanam Project/Stas table for TS 5.1 TO 5.7.xlsx
+++ b/TS Jatai Ghanam Project/Stas table for TS 5.1 TO 5.7.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68D67B31-A93F-4B03-9899-BD1F13A42DDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="5.1" sheetId="15" r:id="rId1"/>
@@ -20033,7 +20033,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="2:12" ht="102" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:12" ht="89.25" x14ac:dyDescent="0.2">
       <c r="B2" s="4" t="s">
         <v>12</v>
       </c>
